--- a/data/trans_orig/P16A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168463</t>
+          <t>171450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215724</t>
+          <t>219999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388106</t>
+          <t>390453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>453879</t>
+          <t>454023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>566979</t>
+          <t>568318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>656377</t>
+          <t>654825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>815999</t>
+          <t>811724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>863260</t>
+          <t>860273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>861234</t>
+          <t>861090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>927007</t>
+          <t>924660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1690458</t>
+          <t>1692010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1779856</t>
+          <t>1778517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174053</t>
+          <t>174258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227635</t>
+          <t>227950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>267052</t>
+          <t>266050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329141</t>
+          <t>328419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>455348</t>
+          <t>459096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>534821</t>
+          <t>539443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1464759</t>
+          <t>1464444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1518341</t>
+          <t>1518136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1258532</t>
+          <t>1259254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1320621</t>
+          <t>1321623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2745246</t>
+          <t>2740624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2824719</t>
+          <t>2820971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50100</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>81638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>109608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132347</t>
+          <t>133445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179694</t>
+          <t>179536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472123</t>
+          <t>469770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501308</t>
+          <t>500952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>366462</t>
+          <t>366804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401430</t>
+          <t>401314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848126</t>
+          <t>848284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>895473</t>
+          <t>894375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>419332</t>
+          <t>419788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>499643</t>
+          <t>494030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>760960</t>
+          <t>758119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>859025</t>
+          <t>857376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1199751</t>
+          <t>1197256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1327515</t>
+          <t>1327501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2775882</t>
+          <t>2781495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2856193</t>
+          <t>2855737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2520172</t>
+          <t>2521821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2618237</t>
+          <t>2621078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5327207</t>
+          <t>5327221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5454971</t>
+          <t>5457466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>212128</t>
+          <t>214424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269387</t>
+          <t>269206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>511849</t>
+          <t>507869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>583391</t>
+          <t>583240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>740158</t>
+          <t>738572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>831530</t>
+          <t>834168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>704441</t>
+          <t>704622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>761700</t>
+          <t>759404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>750136</t>
+          <t>750287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>821678</t>
+          <t>825658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1475825</t>
+          <t>1473187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1567197</t>
+          <t>1568783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>282858</t>
+          <t>283316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351503</t>
+          <t>351248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>475870</t>
+          <t>482262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>553081</t>
+          <t>557171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>784088</t>
+          <t>785243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>893125</t>
+          <t>891759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608519</t>
+          <t>1608774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1677164</t>
+          <t>1676706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1202653</t>
+          <t>1198563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1279864</t>
+          <t>1273472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2822631</t>
+          <t>2823997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2931668</t>
+          <t>2930513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>67874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104201</t>
+          <t>102678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143464</t>
+          <t>142552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148702</t>
+          <t>149854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201051</t>
+          <t>198990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412706</t>
+          <t>412458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441903</t>
+          <t>440363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314190</t>
+          <t>315102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353453</t>
+          <t>354976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>736935</t>
+          <t>738996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>789284</t>
+          <t>788132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565558</t>
+          <t>567120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>657445</t>
+          <t>658773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1127197</t>
+          <t>1127773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1245441</t>
+          <t>1249727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1721752</t>
+          <t>1723524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1868573</t>
+          <t>1877624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2756737</t>
+          <t>2755409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2848624</t>
+          <t>2847062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2301475</t>
+          <t>2297189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2419719</t>
+          <t>2419143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5092525</t>
+          <t>5083474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5239346</t>
+          <t>5237574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160679</t>
+          <t>158165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205423</t>
+          <t>203600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381947</t>
+          <t>381242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>447259</t>
+          <t>450050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>554312</t>
+          <t>555733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>631910</t>
+          <t>635322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>548924</t>
+          <t>550747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>593668</t>
+          <t>596182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>547401</t>
+          <t>544610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>612713</t>
+          <t>613418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1117097</t>
+          <t>1113685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1194695</t>
+          <t>1193274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>320787</t>
+          <t>318601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390673</t>
+          <t>388743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>501275</t>
+          <t>501243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>580160</t>
+          <t>581821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>834564</t>
+          <t>844524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>953608</t>
+          <t>948660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1685712</t>
+          <t>1687642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1755598</t>
+          <t>1757784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1408140</t>
+          <t>1406479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1487025</t>
+          <t>1487057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3111077</t>
+          <t>3116025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3230121</t>
+          <t>3220161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82413</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121889</t>
+          <t>123847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166685</t>
+          <t>166244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218302</t>
+          <t>218298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272565</t>
+          <t>276237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427345</t>
+          <t>424652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464473</t>
+          <t>464230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382455</t>
+          <t>382896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>427251</t>
+          <t>425293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>823462</t>
+          <t>819790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877725</t>
+          <t>877729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>590958</t>
+          <t>589847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>682996</t>
+          <t>681730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1043301</t>
+          <t>1042122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1160050</t>
+          <t>1155131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1659162</t>
+          <t>1665167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1812683</t>
+          <t>1803398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2694622</t>
+          <t>2695888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2786660</t>
+          <t>2787771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2372050</t>
+          <t>2376969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2488799</t>
+          <t>2489978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5097035</t>
+          <t>5106320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5250556</t>
+          <t>5244551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,9%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158071</t>
+          <t>159057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197665</t>
+          <t>197394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>428449</t>
+          <t>428431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>469970</t>
+          <t>470187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599865</t>
+          <t>595828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>656546</t>
+          <t>655960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>317273</t>
+          <t>317544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>356867</t>
+          <t>355881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282658</t>
+          <t>282441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324179</t>
+          <t>324197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>611020</t>
+          <t>611606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667701</t>
+          <t>671738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>323806</t>
+          <t>329483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>544106</t>
+          <t>541441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>718138</t>
+          <t>722405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1251007</t>
+          <t>1252702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1144664</t>
+          <t>1139236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1852083</t>
+          <t>1821342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1746221</t>
+          <t>1748886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1966521</t>
+          <t>1960844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>986138</t>
+          <t>984443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1519007</t>
+          <t>1514740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2675389</t>
+          <t>2706130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3382808</t>
+          <t>3388236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106845</t>
+          <t>108457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152427</t>
+          <t>153057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174257</t>
+          <t>177093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217334</t>
+          <t>218189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>298144</t>
+          <t>295392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357800</t>
+          <t>357009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494196</t>
+          <t>493566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539778</t>
+          <t>538166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443129</t>
+          <t>442274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>486206</t>
+          <t>483370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>949286</t>
+          <t>950077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008942</t>
+          <t>1011694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>614117</t>
+          <t>603814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>858275</t>
+          <t>856115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1377561</t>
+          <t>1376471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1982829</t>
+          <t>1877159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2067673</t>
+          <t>2062801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2733240</t>
+          <t>2735279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2593614</t>
+          <t>2595774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2837772</t>
+          <t>2848075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1667407</t>
+          <t>1773077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2272675</t>
+          <t>2273765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4368885</t>
+          <t>4366846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5034452</t>
+          <t>5039324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171450</t>
+          <t>167467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>219999</t>
+          <t>216545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>390453</t>
+          <t>384019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>454023</t>
+          <t>454743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>568318</t>
+          <t>569882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654825</t>
+          <t>656119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>811724</t>
+          <t>815178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>860273</t>
+          <t>864256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>861090</t>
+          <t>860370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>924660</t>
+          <t>931094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1692010</t>
+          <t>1690716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1778517</t>
+          <t>1776953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174258</t>
+          <t>172069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227950</t>
+          <t>225699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266050</t>
+          <t>264843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328419</t>
+          <t>328028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459096</t>
+          <t>453849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>539443</t>
+          <t>539451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1464444</t>
+          <t>1466695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1518136</t>
+          <t>1520325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1259254</t>
+          <t>1259645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1321623</t>
+          <t>1322830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2740624</t>
+          <t>2740616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2820971</t>
+          <t>2826218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>49935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81638</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>76621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109608</t>
+          <t>109728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133445</t>
+          <t>134641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179536</t>
+          <t>179878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469770</t>
+          <t>472456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500952</t>
+          <t>501473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>366804</t>
+          <t>366684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401314</t>
+          <t>399791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848284</t>
+          <t>847942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>894375</t>
+          <t>893179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>494030</t>
+          <t>496828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>758119</t>
+          <t>752583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>857376</t>
+          <t>853098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1197256</t>
+          <t>1194525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1327501</t>
+          <t>1326086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2781495</t>
+          <t>2778697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2855737</t>
+          <t>2856729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2521821</t>
+          <t>2526099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2621078</t>
+          <t>2626614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5327221</t>
+          <t>5328636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5457466</t>
+          <t>5460197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>214424</t>
+          <t>212062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269206</t>
+          <t>266478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>507869</t>
+          <t>509085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>583240</t>
+          <t>583849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>738572</t>
+          <t>737272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>834168</t>
+          <t>831048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>704622</t>
+          <t>707350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>759404</t>
+          <t>761766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>750287</t>
+          <t>749678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>825658</t>
+          <t>824442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1473187</t>
+          <t>1476307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1568783</t>
+          <t>1570083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283316</t>
+          <t>285831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351248</t>
+          <t>353911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>482262</t>
+          <t>480197</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>557171</t>
+          <t>555837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>785243</t>
+          <t>782829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>891759</t>
+          <t>890856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608774</t>
+          <t>1606111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676706</t>
+          <t>1674191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1198563</t>
+          <t>1199897</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1273472</t>
+          <t>1275537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2823997</t>
+          <t>2824900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2930513</t>
+          <t>2932927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39969</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102678</t>
+          <t>102712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142552</t>
+          <t>142872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149854</t>
+          <t>150642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>200843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412458</t>
+          <t>413345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440363</t>
+          <t>441182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315102</t>
+          <t>314782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354976</t>
+          <t>354942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>738996</t>
+          <t>737143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788132</t>
+          <t>787344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567120</t>
+          <t>561817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658773</t>
+          <t>655811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1127773</t>
+          <t>1128738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1249727</t>
+          <t>1246251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1723524</t>
+          <t>1730663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1877624</t>
+          <t>1877579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2755409</t>
+          <t>2758371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2847062</t>
+          <t>2852365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2297189</t>
+          <t>2300665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2419143</t>
+          <t>2418178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5083474</t>
+          <t>5083519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5237574</t>
+          <t>5230435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158165</t>
+          <t>158097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203600</t>
+          <t>203960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381242</t>
+          <t>381802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>450050</t>
+          <t>448276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>555733</t>
+          <t>554627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>635322</t>
+          <t>635421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>550747</t>
+          <t>550387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>596182</t>
+          <t>596250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>544610</t>
+          <t>546384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613418</t>
+          <t>612858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1113685</t>
+          <t>1113586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1193274</t>
+          <t>1194380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318601</t>
+          <t>321862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>388743</t>
+          <t>395888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>501243</t>
+          <t>504744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>581821</t>
+          <t>584866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>844524</t>
+          <t>843533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>948660</t>
+          <t>948453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1687642</t>
+          <t>1680497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1757784</t>
+          <t>1754523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1406479</t>
+          <t>1403434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1487057</t>
+          <t>1483556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3116025</t>
+          <t>3116232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3220161</t>
+          <t>3221152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82656</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122234</t>
+          <t>120855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123847</t>
+          <t>124621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166244</t>
+          <t>167135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218298</t>
+          <t>216915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276237</t>
+          <t>272383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424652</t>
+          <t>426031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464230</t>
+          <t>464439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382896</t>
+          <t>382005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425293</t>
+          <t>424519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>819790</t>
+          <t>823644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877729</t>
+          <t>879112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>589847</t>
+          <t>590081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>681730</t>
+          <t>685276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1042122</t>
+          <t>1047213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1155131</t>
+          <t>1155565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1665167</t>
+          <t>1663281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1803398</t>
+          <t>1812302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2695888</t>
+          <t>2692342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2787771</t>
+          <t>2787537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2376969</t>
+          <t>2376535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2489978</t>
+          <t>2484887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5106320</t>
+          <t>5097416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5244551</t>
+          <t>5246437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>191112</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159057</t>
+          <t>169772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197394</t>
+          <t>213609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>449881</t>
+          <t>484423</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>428431</t>
+          <t>462647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>470187</t>
+          <t>505399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>626637</t>
+          <t>675535</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>595828</t>
+          <t>642682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655960</t>
+          <t>707289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>338182</t>
+          <t>387417</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>317544</t>
+          <t>364920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355881</t>
+          <t>408757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>302747</t>
+          <t>336289</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282441</t>
+          <t>315313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324197</t>
+          <t>358065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>640929</t>
+          <t>723706</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>611606</t>
+          <t>691952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671738</t>
+          <t>756559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752628</t>
+          <t>820712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267566</t>
+          <t>1399241</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>470523</t>
+          <t>505591</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329483</t>
+          <t>460296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>541441</t>
+          <t>551616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>884546</t>
+          <t>750939</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>722405</t>
+          <t>712330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1252702</t>
+          <t>792023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1355069</t>
+          <t>1256531</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1139236</t>
+          <t>1201212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1821342</t>
+          <t>1323888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1819804</t>
+          <t>1724975</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1748886</t>
+          <t>1678950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960844</t>
+          <t>1770270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1352599</t>
+          <t>1419768</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>984443</t>
+          <t>1378684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1514740</t>
+          <t>1458377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3172403</t>
+          <t>3144743</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2706130</t>
+          <t>3077386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3388236</t>
+          <t>3200062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>128330</t>
+          <t>141330</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108457</t>
+          <t>119479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153057</t>
+          <t>166625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>196889</t>
+          <t>215854</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177093</t>
+          <t>194343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218189</t>
+          <t>239110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>325220</t>
+          <t>357184</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295392</t>
+          <t>326033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357009</t>
+          <t>388842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518293</t>
+          <t>570257</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493566</t>
+          <t>544962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538166</t>
+          <t>592108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>463574</t>
+          <t>519023</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442274</t>
+          <t>495767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>483370</t>
+          <t>540534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>981866</t>
+          <t>1089280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>950077</t>
+          <t>1057622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1011694</t>
+          <t>1120431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>775610</t>
+          <t>838034</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>603814</t>
+          <t>787408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>856115</t>
+          <t>892626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1531316</t>
+          <t>1451216</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1376471</t>
+          <t>1399468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1877159</t>
+          <t>1502415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2306926</t>
+          <t>2289249</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2062801</t>
+          <t>2218670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2735279</t>
+          <t>2366218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2676279</t>
+          <t>2682649</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2595774</t>
+          <t>2628057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2848075</t>
+          <t>2733275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2118920</t>
+          <t>2275081</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1773077</t>
+          <t>2223882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2273765</t>
+          <t>2326829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4795199</t>
+          <t>4957730</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4366846</t>
+          <t>4880761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5039324</t>
+          <t>5028309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650236</t>
+          <t>3726297</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7102125</t>
+          <t>7246979</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
